--- a/datos/portal_investigacion_unphu.xlsx
+++ b/datos/portal_investigacion_unphu.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\Portal de Investigación UNPHU\portal-investigacion-unphu\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39AB883-F275-4235-A6EC-10334499648A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{B39AB883-F275-4235-A6EC-10334499648A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{249FBBE0-96A7-42AD-8A78-E27BB8725413}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>ID</t>
   </si>
@@ -107,13 +107,31 @@
   </si>
   <si>
     <t>laboratorio.png</t>
+  </si>
+  <si>
+    <t>PUB001</t>
+  </si>
+  <si>
+    <t>Publicacion Cientifica</t>
+  </si>
+  <si>
+    <t>Recursos para publicar, posicionar y difundir tu investigación</t>
+  </si>
+  <si>
+    <t>https://wilintec.github.io/portal-publicacion-cientifica-unphu/</t>
+  </si>
+  <si>
+    <t>Publicacion</t>
+  </si>
+  <si>
+    <t>publica.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -122,6 +140,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -147,10 +171,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -158,8 +183,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -517,15 +546,33 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="32.1" customHeight="1">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -536,9 +583,12 @@
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{A7104E49-56ED-46AC-9889-8FBD0D0B1E50}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>